--- a/results/CB/Summary of changes to Responses.xlsx
+++ b/results/CB/Summary of changes to Responses.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N166"/>
+  <dimension ref="A1:N165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3948,10 +3948,14 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Corrected: ResponseType</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -4000,10 +4004,14 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Corrected: ResponseType</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -4108,10 +4116,14 @@
           <t>GO</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Corrected: ResponseType</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -4471,54 +4483,56 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T19:16:58.918521_yoshi_6.0_Training randomised Type 1.log</t>
+          <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D73" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="E73" t="n">
-        <v>2574</v>
+        <v>2707</v>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>GO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Corrected: ResponseType</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>1469</v>
+        <v>1528</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>45244.81056145292</v>
+        <v>45245.19691450314</v>
       </c>
       <c r="L73" t="n">
-        <v>13.078219</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+        <v>11.45887</v>
+      </c>
+      <c r="M73" t="n">
+        <v>10.27</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Corrected: ResponseTime to NULL</t>
+          <t>Corrected: ResponseTime</t>
         </is>
       </c>
     </row>
@@ -4540,10 +4554,10 @@
         <v>153</v>
       </c>
       <c r="E74" t="n">
-        <v>2707</v>
+        <v>2711</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4561,16 +4575,16 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>45245.19691450314</v>
+        <v>45245.19979635652</v>
       </c>
       <c r="L74" t="n">
-        <v>11.45887</v>
+        <v>11.128929</v>
       </c>
       <c r="M74" t="n">
-        <v>10.27</v>
+        <v>9.81</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -4596,10 +4610,10 @@
         <v>153</v>
       </c>
       <c r="E75" t="n">
-        <v>2711</v>
+        <v>2715</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4617,16 +4631,16 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>45245.19979635652</v>
+        <v>45245.20253195269</v>
       </c>
       <c r="L75" t="n">
-        <v>11.128929</v>
+        <v>16.965951</v>
       </c>
       <c r="M75" t="n">
-        <v>9.81</v>
+        <v>15.25</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -4652,10 +4666,10 @@
         <v>153</v>
       </c>
       <c r="E76" t="n">
-        <v>2715</v>
+        <v>2717</v>
       </c>
       <c r="F76" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4673,16 +4687,16 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>45245.20253195269</v>
+        <v>45245.2051403589</v>
       </c>
       <c r="L76" t="n">
-        <v>16.965951</v>
+        <v>13.855669</v>
       </c>
       <c r="M76" t="n">
-        <v>15.25</v>
+        <v>11.53</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -4708,10 +4722,10 @@
         <v>153</v>
       </c>
       <c r="E77" t="n">
-        <v>2717</v>
+        <v>2720</v>
       </c>
       <c r="F77" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4729,16 +4743,16 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>45245.2051403589</v>
+        <v>45245.20964881693</v>
       </c>
       <c r="L77" t="n">
-        <v>13.855669</v>
+        <v>11.7764</v>
       </c>
       <c r="M77" t="n">
-        <v>11.53</v>
+        <v>11.09</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -4749,25 +4763,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-15T05:22:53.513691_gio_6.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D78" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E78" t="n">
-        <v>2720</v>
+        <v>2729</v>
       </c>
       <c r="F78" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4785,16 +4799,16 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>45245.20964881693</v>
+        <v>45245.23541459804</v>
       </c>
       <c r="L78" t="n">
-        <v>11.7764</v>
+        <v>15.594505</v>
       </c>
       <c r="M78" t="n">
-        <v>11.09</v>
+        <v>10.12</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -4820,10 +4834,10 @@
         <v>154</v>
       </c>
       <c r="E79" t="n">
-        <v>2729</v>
+        <v>2731</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4841,16 +4855,16 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>45245.23541459804</v>
+        <v>45245.23698837094</v>
       </c>
       <c r="L79" t="n">
-        <v>15.594505</v>
+        <v>2.771426</v>
       </c>
       <c r="M79" t="n">
-        <v>10.12</v>
+        <v>9.49</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -4861,25 +4875,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T05:22:53.513691_gio_6.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>clover</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D80" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E80" t="n">
-        <v>2731</v>
+        <v>2812</v>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4897,16 +4911,16 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>1536</v>
+        <v>1570</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>45245.23698837094</v>
+        <v>45245.97316194134</v>
       </c>
       <c r="L80" t="n">
-        <v>2.771426</v>
+        <v>12.315406</v>
       </c>
       <c r="M80" t="n">
-        <v>9.49</v>
+        <v>11.85</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -4932,10 +4946,10 @@
         <v>160</v>
       </c>
       <c r="E81" t="n">
-        <v>2812</v>
+        <v>2813</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4953,16 +4967,16 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>45245.97316194134</v>
+        <v>45245.97406437432</v>
       </c>
       <c r="L81" t="n">
-        <v>12.315406</v>
+        <v>19.183383</v>
       </c>
       <c r="M81" t="n">
-        <v>11.85</v>
+        <v>18.88</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -4988,10 +5002,10 @@
         <v>160</v>
       </c>
       <c r="E82" t="n">
-        <v>2813</v>
+        <v>2815</v>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5009,16 +5023,16 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>45245.97406437432</v>
+        <v>45245.97515698333</v>
       </c>
       <c r="L82" t="n">
-        <v>19.183383</v>
+        <v>12.277386</v>
       </c>
       <c r="M82" t="n">
-        <v>18.88</v>
+        <v>10.94</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -5044,10 +5058,10 @@
         <v>160</v>
       </c>
       <c r="E83" t="n">
-        <v>2815</v>
+        <v>2817</v>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5056,25 +5070,25 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Corrected: ResponseType</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>45245.97515698333</v>
+        <v>45245.97637159583</v>
       </c>
       <c r="L83" t="n">
-        <v>12.277386</v>
+        <v>7.158316</v>
       </c>
       <c r="M83" t="n">
-        <v>10.94</v>
+        <v>30</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -5100,10 +5114,10 @@
         <v>160</v>
       </c>
       <c r="E84" t="n">
-        <v>2817</v>
+        <v>2819</v>
       </c>
       <c r="F84" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5112,25 +5126,25 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Corrected: ResponseType</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>45245.97637159583</v>
+        <v>45245.97771395952</v>
       </c>
       <c r="L84" t="n">
-        <v>7.158316</v>
+        <v>12.639678</v>
       </c>
       <c r="M84" t="n">
-        <v>30</v>
+        <v>11.93</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -5156,10 +5170,10 @@
         <v>160</v>
       </c>
       <c r="E85" t="n">
-        <v>2819</v>
+        <v>2821</v>
       </c>
       <c r="F85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5177,16 +5191,16 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>45245.97771395952</v>
+        <v>45245.97967322704</v>
       </c>
       <c r="L85" t="n">
-        <v>12.639678</v>
+        <v>12.105527</v>
       </c>
       <c r="M85" t="n">
-        <v>11.93</v>
+        <v>10.48</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -5212,10 +5226,10 @@
         <v>160</v>
       </c>
       <c r="E86" t="n">
-        <v>2821</v>
+        <v>2823</v>
       </c>
       <c r="F86" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5224,25 +5238,25 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Corrected: ResponseType</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>45245.97967322704</v>
+        <v>45245.98137506161</v>
       </c>
       <c r="L86" t="n">
-        <v>12.105527</v>
+        <v>18.461872</v>
       </c>
       <c r="M86" t="n">
-        <v>10.48</v>
+        <v>30</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -5268,10 +5282,10 @@
         <v>160</v>
       </c>
       <c r="E87" t="n">
-        <v>2823</v>
+        <v>2826</v>
       </c>
       <c r="F87" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5289,13 +5303,13 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>45245.98137506161</v>
+        <v>45245.98421429555</v>
       </c>
       <c r="L87" t="n">
-        <v>18.461872</v>
+        <v>14.768316</v>
       </c>
       <c r="M87" t="n">
         <v>30</v>
@@ -5309,25 +5323,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
+          <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>clover</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D88" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E88" t="n">
-        <v>2826</v>
+        <v>2872</v>
       </c>
       <c r="F88" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5336,25 +5350,25 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Corrected: ResponseType</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>1577</v>
+        <v>1597</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>45245.98421429555</v>
+        <v>45246.38545727215</v>
       </c>
       <c r="L88" t="n">
-        <v>14.768316</v>
+        <v>11.915961</v>
       </c>
       <c r="M88" t="n">
-        <v>30</v>
+        <v>10.01</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -5380,10 +5394,10 @@
         <v>164</v>
       </c>
       <c r="E89" t="n">
-        <v>2872</v>
+        <v>2874</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5401,16 +5415,16 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>45246.38545727215</v>
+        <v>45246.38723355257</v>
       </c>
       <c r="L89" t="n">
-        <v>11.915961</v>
+        <v>11.136765</v>
       </c>
       <c r="M89" t="n">
-        <v>10.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -5436,10 +5450,10 @@
         <v>164</v>
       </c>
       <c r="E90" t="n">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5457,16 +5471,16 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>45246.38723355257</v>
+        <v>45246.38822015277</v>
       </c>
       <c r="L90" t="n">
-        <v>11.136765</v>
+        <v>21.932665</v>
       </c>
       <c r="M90" t="n">
-        <v>9.800000000000001</v>
+        <v>20.87</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -5492,10 +5506,10 @@
         <v>164</v>
       </c>
       <c r="E91" t="n">
-        <v>2875</v>
+        <v>2877</v>
       </c>
       <c r="F91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5513,16 +5527,16 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>45246.38822015277</v>
+        <v>45246.38916890263</v>
       </c>
       <c r="L91" t="n">
-        <v>21.932665</v>
+        <v>11.315722</v>
       </c>
       <c r="M91" t="n">
-        <v>20.87</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -5548,10 +5562,10 @@
         <v>164</v>
       </c>
       <c r="E92" t="n">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5569,16 +5583,16 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>45246.38916890263</v>
+        <v>45246.38994094116</v>
       </c>
       <c r="L92" t="n">
-        <v>11.315722</v>
+        <v>12.809741</v>
       </c>
       <c r="M92" t="n">
-        <v>8.949999999999999</v>
+        <v>10.57</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -5604,10 +5618,10 @@
         <v>164</v>
       </c>
       <c r="E93" t="n">
-        <v>2878</v>
+        <v>2881</v>
       </c>
       <c r="F93" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5625,16 +5639,16 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>45246.38994094116</v>
+        <v>45246.39262756678</v>
       </c>
       <c r="L93" t="n">
-        <v>12.809741</v>
+        <v>11.948804</v>
       </c>
       <c r="M93" t="n">
-        <v>10.57</v>
+        <v>11.14</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -5660,10 +5674,10 @@
         <v>164</v>
       </c>
       <c r="E94" t="n">
-        <v>2881</v>
+        <v>2883</v>
       </c>
       <c r="F94" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5681,16 +5695,16 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>45246.39262756678</v>
+        <v>45246.39422212101</v>
       </c>
       <c r="L94" t="n">
-        <v>11.948804</v>
+        <v>15.359037</v>
       </c>
       <c r="M94" t="n">
-        <v>11.14</v>
+        <v>13.46</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -5716,10 +5730,10 @@
         <v>164</v>
       </c>
       <c r="E95" t="n">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="F95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5737,16 +5751,16 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>45246.39422212101</v>
+        <v>45246.39476618616</v>
       </c>
       <c r="L95" t="n">
-        <v>15.359037</v>
+        <v>11.135881</v>
       </c>
       <c r="M95" t="n">
-        <v>13.46</v>
+        <v>8.49</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -5757,7 +5771,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5769,13 +5783,13 @@
         <v>16</v>
       </c>
       <c r="D96" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E96" t="n">
-        <v>2884</v>
+        <v>2962</v>
       </c>
       <c r="F96" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -5793,16 +5807,16 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>1604</v>
+        <v>1645</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>45246.39476618616</v>
+        <v>45246.65972760375</v>
       </c>
       <c r="L96" t="n">
-        <v>11.135881</v>
+        <v>10.949954</v>
       </c>
       <c r="M96" t="n">
-        <v>8.49</v>
+        <v>11.01</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -5828,10 +5842,10 @@
         <v>170</v>
       </c>
       <c r="E97" t="n">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5849,16 +5863,16 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>45246.65972760375</v>
+        <v>45246.66071754423</v>
       </c>
       <c r="L97" t="n">
-        <v>10.949954</v>
+        <v>20.325943</v>
       </c>
       <c r="M97" t="n">
-        <v>11.01</v>
+        <v>12.99</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -5884,10 +5898,10 @@
         <v>170</v>
       </c>
       <c r="E98" t="n">
-        <v>2963</v>
+        <v>2966</v>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5905,16 +5919,16 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>45246.66071754423</v>
+        <v>45246.6620723353</v>
       </c>
       <c r="L98" t="n">
-        <v>20.325943</v>
+        <v>12.953665</v>
       </c>
       <c r="M98" t="n">
-        <v>12.99</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -5940,10 +5954,10 @@
         <v>170</v>
       </c>
       <c r="E99" t="n">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="F99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5961,16 +5975,16 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>45246.6620723353</v>
+        <v>45246.66282455371</v>
       </c>
       <c r="L99" t="n">
-        <v>12.953665</v>
+        <v>14.671365</v>
       </c>
       <c r="M99" t="n">
-        <v>9.869999999999999</v>
+        <v>12.41</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -5996,10 +6010,10 @@
         <v>170</v>
       </c>
       <c r="E100" t="n">
-        <v>2967</v>
+        <v>2970</v>
       </c>
       <c r="F100" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6017,16 +6031,16 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>45246.66282455371</v>
+        <v>45246.66478124687</v>
       </c>
       <c r="L100" t="n">
-        <v>14.671365</v>
+        <v>11.177949</v>
       </c>
       <c r="M100" t="n">
-        <v>12.41</v>
+        <v>10.4</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -6052,10 +6066,10 @@
         <v>170</v>
       </c>
       <c r="E101" t="n">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="F101" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -6073,16 +6087,16 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>45246.66478124687</v>
+        <v>45246.66668340648</v>
       </c>
       <c r="L101" t="n">
-        <v>11.177949</v>
+        <v>9.281331</v>
       </c>
       <c r="M101" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -6108,10 +6122,10 @@
         <v>170</v>
       </c>
       <c r="E102" t="n">
-        <v>2973</v>
+        <v>2975</v>
       </c>
       <c r="F102" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6129,16 +6143,16 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>45246.66668340648</v>
+        <v>45246.66821096941</v>
       </c>
       <c r="L102" t="n">
-        <v>9.281331</v>
+        <v>14.62976</v>
       </c>
       <c r="M102" t="n">
-        <v>10.2</v>
+        <v>11.39</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -6149,25 +6163,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D103" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E103" t="n">
-        <v>2975</v>
+        <v>2977</v>
       </c>
       <c r="F103" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6185,16 +6199,16 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>45246.66821096941</v>
+        <v>45246.74725903512</v>
       </c>
       <c r="L103" t="n">
-        <v>14.62976</v>
+        <v>2.803082</v>
       </c>
       <c r="M103" t="n">
-        <v>11.39</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -6220,10 +6234,10 @@
         <v>171</v>
       </c>
       <c r="E104" t="n">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -6232,25 +6246,25 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Corrected: ResponseType</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>45246.74725903512</v>
+        <v>45246.74744415817</v>
       </c>
       <c r="L104" t="n">
-        <v>2.803082</v>
+        <v>3.985152</v>
       </c>
       <c r="M104" t="n">
-        <v>9.289999999999999</v>
+        <v>30</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -6276,10 +6290,10 @@
         <v>171</v>
       </c>
       <c r="E105" t="n">
-        <v>2978</v>
+        <v>2981</v>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6288,25 +6302,25 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Corrected: ResponseType</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>45246.74744415817</v>
+        <v>45246.74861468578</v>
       </c>
       <c r="L105" t="n">
-        <v>3.985152</v>
+        <v>10.621431</v>
       </c>
       <c r="M105" t="n">
-        <v>30</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -6332,10 +6346,10 @@
         <v>171</v>
       </c>
       <c r="E106" t="n">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="F106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6353,16 +6367,16 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>45246.74861468578</v>
+        <v>45246.74937147988</v>
       </c>
       <c r="L106" t="n">
-        <v>10.621431</v>
+        <v>11.855038</v>
       </c>
       <c r="M106" t="n">
-        <v>9.869999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -6388,10 +6402,10 @@
         <v>171</v>
       </c>
       <c r="E107" t="n">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="F107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6400,25 +6414,25 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Corrected: ResponseType</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>45246.74937147988</v>
+        <v>45246.75039967555</v>
       </c>
       <c r="L107" t="n">
-        <v>11.855038</v>
+        <v>29.822653</v>
       </c>
       <c r="M107" t="n">
-        <v>9.33</v>
+        <v>30</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -6444,10 +6458,10 @@
         <v>171</v>
       </c>
       <c r="E108" t="n">
-        <v>2983</v>
+        <v>2985</v>
       </c>
       <c r="F108" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6456,25 +6470,25 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Corrected: ResponseType</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>45246.75039967555</v>
+        <v>45246.75125015287</v>
       </c>
       <c r="L108" t="n">
-        <v>29.822653</v>
+        <v>10.951413</v>
       </c>
       <c r="M108" t="n">
-        <v>30</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -6500,10 +6514,10 @@
         <v>171</v>
       </c>
       <c r="E109" t="n">
-        <v>2985</v>
+        <v>2987</v>
       </c>
       <c r="F109" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6512,25 +6526,25 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Corrected: ResponseType</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>45246.75125015287</v>
+        <v>45246.75271800184</v>
       </c>
       <c r="L109" t="n">
-        <v>10.951413</v>
+        <v>23.494118</v>
       </c>
       <c r="M109" t="n">
-        <v>9.220000000000001</v>
+        <v>30</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -6556,10 +6570,10 @@
         <v>171</v>
       </c>
       <c r="E110" t="n">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="F110" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6568,25 +6582,25 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Corrected: ResponseType</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>45246.75271800184</v>
+        <v>45246.75321231485</v>
       </c>
       <c r="L110" t="n">
-        <v>23.494118</v>
+        <v>11.419047</v>
       </c>
       <c r="M110" t="n">
-        <v>30</v>
+        <v>9.43</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -6612,10 +6626,10 @@
         <v>171</v>
       </c>
       <c r="E111" t="n">
-        <v>2988</v>
+        <v>2990</v>
       </c>
       <c r="F111" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6633,16 +6647,16 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>45246.75321231485</v>
+        <v>45246.75460966777</v>
       </c>
       <c r="L111" t="n">
-        <v>11.419047</v>
+        <v>11.516777</v>
       </c>
       <c r="M111" t="n">
-        <v>9.43</v>
+        <v>9.66</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -6653,25 +6667,25 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>smudge</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D112" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E112" t="n">
-        <v>2990</v>
+        <v>3007</v>
       </c>
       <c r="F112" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6689,16 +6703,16 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>1660</v>
+        <v>1667</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>45246.75460966777</v>
+        <v>45246.85536228023</v>
       </c>
       <c r="L112" t="n">
-        <v>11.516777</v>
+        <v>11.557341</v>
       </c>
       <c r="M112" t="n">
-        <v>9.66</v>
+        <v>10.14</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -6724,10 +6738,10 @@
         <v>173</v>
       </c>
       <c r="E113" t="n">
-        <v>3007</v>
+        <v>3011</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6745,16 +6759,16 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>45246.85536228023</v>
+        <v>45246.85797114565</v>
       </c>
       <c r="L113" t="n">
-        <v>11.557341</v>
+        <v>11.216621</v>
       </c>
       <c r="M113" t="n">
-        <v>10.14</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -6780,10 +6794,10 @@
         <v>173</v>
       </c>
       <c r="E114" t="n">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="F114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6801,16 +6815,16 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>45246.85797114565</v>
+        <v>45246.85893970131</v>
       </c>
       <c r="L114" t="n">
-        <v>11.216621</v>
+        <v>12.284103</v>
       </c>
       <c r="M114" t="n">
-        <v>9.869999999999999</v>
+        <v>10.87</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
@@ -6836,10 +6850,10 @@
         <v>173</v>
       </c>
       <c r="E115" t="n">
-        <v>3012</v>
+        <v>3015</v>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -6857,16 +6871,16 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>45246.85893970131</v>
+        <v>45246.86099143763</v>
       </c>
       <c r="L115" t="n">
-        <v>12.284103</v>
+        <v>12.854925</v>
       </c>
       <c r="M115" t="n">
-        <v>10.87</v>
+        <v>10.22</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -6892,10 +6906,10 @@
         <v>173</v>
       </c>
       <c r="E116" t="n">
-        <v>3015</v>
+        <v>3018</v>
       </c>
       <c r="F116" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6913,16 +6927,16 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>45246.86099143763</v>
+        <v>45246.86313866416</v>
       </c>
       <c r="L116" t="n">
-        <v>12.854925</v>
+        <v>12.416385</v>
       </c>
       <c r="M116" t="n">
-        <v>10.22</v>
+        <v>10.87</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
@@ -6948,10 +6962,10 @@
         <v>173</v>
       </c>
       <c r="E117" t="n">
-        <v>3018</v>
+        <v>3020</v>
       </c>
       <c r="F117" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6969,13 +6983,13 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>45246.86313866416</v>
+        <v>45246.86498953704</v>
       </c>
       <c r="L117" t="n">
-        <v>12.416385</v>
+        <v>12.741076</v>
       </c>
       <c r="M117" t="n">
         <v>10.87</v>
@@ -6989,25 +7003,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>smudge</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D118" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E118" t="n">
-        <v>3020</v>
+        <v>3022</v>
       </c>
       <c r="F118" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -7025,16 +7039,16 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>45246.86498953704</v>
+        <v>45246.88879245762</v>
       </c>
       <c r="L118" t="n">
-        <v>12.741076</v>
+        <v>12.080123</v>
       </c>
       <c r="M118" t="n">
-        <v>10.87</v>
+        <v>7.99</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -7060,10 +7074,10 @@
         <v>174</v>
       </c>
       <c r="E119" t="n">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -7072,25 +7086,25 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Corrected: ResponseType</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>45246.88879245762</v>
+        <v>45246.88976528713</v>
       </c>
       <c r="L119" t="n">
-        <v>12.080123</v>
+        <v>26.447223</v>
       </c>
       <c r="M119" t="n">
-        <v>7.99</v>
+        <v>30</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -7116,10 +7130,10 @@
         <v>174</v>
       </c>
       <c r="E120" t="n">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="F120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -7128,25 +7142,25 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Corrected: ResponseType</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>45246.88976528713</v>
+        <v>45246.89026023034</v>
       </c>
       <c r="L120" t="n">
-        <v>26.447223</v>
+        <v>11.690637</v>
       </c>
       <c r="M120" t="n">
-        <v>30</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -7172,10 +7186,10 @@
         <v>174</v>
       </c>
       <c r="E121" t="n">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -7193,16 +7207,16 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>45246.89026023034</v>
+        <v>45246.89117958806</v>
       </c>
       <c r="L121" t="n">
-        <v>11.690637</v>
+        <v>19.769017</v>
       </c>
       <c r="M121" t="n">
-        <v>9.140000000000001</v>
+        <v>18.01</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -7228,10 +7242,10 @@
         <v>174</v>
       </c>
       <c r="E122" t="n">
-        <v>3025</v>
+        <v>3027</v>
       </c>
       <c r="F122" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -7249,16 +7263,16 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>45246.89117958806</v>
+        <v>45246.89221943357</v>
       </c>
       <c r="L122" t="n">
-        <v>19.769017</v>
+        <v>14.787294</v>
       </c>
       <c r="M122" t="n">
-        <v>18.01</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -7284,10 +7298,10 @@
         <v>174</v>
       </c>
       <c r="E123" t="n">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="F123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -7305,16 +7319,16 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>45246.89221943357</v>
+        <v>45246.89300805015</v>
       </c>
       <c r="L123" t="n">
-        <v>14.787294</v>
+        <v>11.017646</v>
       </c>
       <c r="M123" t="n">
-        <v>9.220000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -7340,10 +7354,10 @@
         <v>174</v>
       </c>
       <c r="E124" t="n">
-        <v>3028</v>
+        <v>3031</v>
       </c>
       <c r="F124" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -7361,16 +7375,16 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>45246.89300805015</v>
+        <v>45246.89526973582</v>
       </c>
       <c r="L124" t="n">
-        <v>11.017646</v>
+        <v>12.865251</v>
       </c>
       <c r="M124" t="n">
-        <v>9.550000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -7396,10 +7410,10 @@
         <v>174</v>
       </c>
       <c r="E125" t="n">
-        <v>3031</v>
+        <v>3034</v>
       </c>
       <c r="F125" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -7417,16 +7431,16 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>45246.89526973582</v>
+        <v>45246.89749475177</v>
       </c>
       <c r="L125" t="n">
-        <v>12.865251</v>
+        <v>11.335065</v>
       </c>
       <c r="M125" t="n">
-        <v>10.13</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -7437,25 +7451,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D126" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E126" t="n">
-        <v>3034</v>
+        <v>3037</v>
       </c>
       <c r="F126" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -7473,16 +7487,16 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>45246.89749475177</v>
+        <v>45246.91916123396</v>
       </c>
       <c r="L126" t="n">
-        <v>11.335065</v>
+        <v>13.056877</v>
       </c>
       <c r="M126" t="n">
-        <v>9.630000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -7508,10 +7522,10 @@
         <v>175</v>
       </c>
       <c r="E127" t="n">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -7529,16 +7543,16 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>45246.91916123396</v>
+        <v>45246.91997735655</v>
       </c>
       <c r="L127" t="n">
-        <v>13.056877</v>
+        <v>26.150554</v>
       </c>
       <c r="M127" t="n">
-        <v>8.23</v>
+        <v>25.39</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -7564,10 +7578,10 @@
         <v>175</v>
       </c>
       <c r="E128" t="n">
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -7585,16 +7599,16 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>45246.91997735655</v>
+        <v>45246.92046205697</v>
       </c>
       <c r="L128" t="n">
-        <v>26.150554</v>
+        <v>11.702376</v>
       </c>
       <c r="M128" t="n">
-        <v>25.39</v>
+        <v>8.16</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -7620,10 +7634,10 @@
         <v>175</v>
       </c>
       <c r="E129" t="n">
-        <v>3039</v>
+        <v>3042</v>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -7641,16 +7655,16 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>45246.92046205697</v>
+        <v>45246.92240427351</v>
       </c>
       <c r="L129" t="n">
-        <v>11.702376</v>
+        <v>10.042624</v>
       </c>
       <c r="M129" t="n">
-        <v>8.16</v>
+        <v>8.82</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -7676,10 +7690,10 @@
         <v>175</v>
       </c>
       <c r="E130" t="n">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="F130" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -7697,16 +7711,16 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>45246.92240427351</v>
+        <v>45246.92328370611</v>
       </c>
       <c r="L130" t="n">
-        <v>10.042624</v>
+        <v>10.822374</v>
       </c>
       <c r="M130" t="n">
-        <v>8.82</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -7732,10 +7746,10 @@
         <v>175</v>
       </c>
       <c r="E131" t="n">
-        <v>3043</v>
+        <v>3046</v>
       </c>
       <c r="F131" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -7753,16 +7767,16 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>45246.92328370611</v>
+        <v>45246.92514060332</v>
       </c>
       <c r="L131" t="n">
-        <v>10.822374</v>
+        <v>10.357841</v>
       </c>
       <c r="M131" t="n">
-        <v>9.140000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -7788,10 +7802,10 @@
         <v>175</v>
       </c>
       <c r="E132" t="n">
-        <v>3046</v>
+        <v>3049</v>
       </c>
       <c r="F132" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -7809,16 +7823,16 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>45246.92514060332</v>
+        <v>45246.92730989179</v>
       </c>
       <c r="L132" t="n">
-        <v>10.357841</v>
+        <v>12.504554</v>
       </c>
       <c r="M132" t="n">
-        <v>8.949999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -7829,25 +7843,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D133" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E133" t="n">
-        <v>3049</v>
+        <v>3052</v>
       </c>
       <c r="F133" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -7865,16 +7879,16 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>45246.92730989179</v>
+        <v>45247.00002677304</v>
       </c>
       <c r="L133" t="n">
-        <v>12.504554</v>
+        <v>20.307244</v>
       </c>
       <c r="M133" t="n">
-        <v>9.08</v>
+        <v>7.62</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -7900,10 +7914,10 @@
         <v>176</v>
       </c>
       <c r="E134" t="n">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -7921,16 +7935,16 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>45247.00002677304</v>
+        <v>45247.00102358646</v>
       </c>
       <c r="L134" t="n">
-        <v>20.307244</v>
+        <v>17.336063</v>
       </c>
       <c r="M134" t="n">
-        <v>7.62</v>
+        <v>15.96</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
@@ -7956,10 +7970,10 @@
         <v>176</v>
       </c>
       <c r="E135" t="n">
-        <v>3053</v>
+        <v>3054</v>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -7977,16 +7991,16 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>45247.00102358646</v>
+        <v>45247.00141032288</v>
       </c>
       <c r="L135" t="n">
-        <v>17.336063</v>
+        <v>10.338043</v>
       </c>
       <c r="M135" t="n">
-        <v>15.96</v>
+        <v>8.56</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -8012,10 +8026,10 @@
         <v>176</v>
       </c>
       <c r="E136" t="n">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -8033,16 +8047,16 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>45247.00141032288</v>
+        <v>45247.00210321089</v>
       </c>
       <c r="L136" t="n">
-        <v>10.338043</v>
+        <v>12.772846</v>
       </c>
       <c r="M136" t="n">
-        <v>8.56</v>
+        <v>11.54</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -8068,10 +8082,10 @@
         <v>176</v>
       </c>
       <c r="E137" t="n">
-        <v>3055</v>
+        <v>3058</v>
       </c>
       <c r="F137" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -8089,16 +8103,16 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>45247.00210321089</v>
+        <v>45247.0039468522</v>
       </c>
       <c r="L137" t="n">
-        <v>12.772846</v>
+        <v>9.625442</v>
       </c>
       <c r="M137" t="n">
-        <v>11.54</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -8124,10 +8138,10 @@
         <v>176</v>
       </c>
       <c r="E138" t="n">
-        <v>3058</v>
+        <v>3061</v>
       </c>
       <c r="F138" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -8145,16 +8159,16 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>45247.0039468522</v>
+        <v>45247.00617325243</v>
       </c>
       <c r="L138" t="n">
-        <v>9.625442</v>
+        <v>11.337528</v>
       </c>
       <c r="M138" t="n">
-        <v>8.609999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -8180,10 +8194,10 @@
         <v>176</v>
       </c>
       <c r="E139" t="n">
-        <v>3061</v>
+        <v>3064</v>
       </c>
       <c r="F139" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -8201,16 +8215,16 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>45247.00617325243</v>
+        <v>45247.00889589202</v>
       </c>
       <c r="L139" t="n">
-        <v>11.337528</v>
+        <v>9.544181</v>
       </c>
       <c r="M139" t="n">
-        <v>9.6</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
@@ -8221,7 +8235,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
+          <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8233,13 +8247,13 @@
         <v>18</v>
       </c>
       <c r="D140" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E140" t="n">
-        <v>3064</v>
+        <v>3127</v>
       </c>
       <c r="F140" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8257,16 +8271,16 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>1694</v>
+        <v>1718</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>45247.00889589202</v>
+        <v>45247.17124424849</v>
       </c>
       <c r="L140" t="n">
-        <v>9.544181</v>
+        <v>11.758066</v>
       </c>
       <c r="M140" t="n">
-        <v>8.460000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
@@ -8292,10 +8306,10 @@
         <v>181</v>
       </c>
       <c r="E141" t="n">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -8313,16 +8327,16 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>45247.17124424849</v>
+        <v>45247.17200462607</v>
       </c>
       <c r="L141" t="n">
-        <v>11.758066</v>
+        <v>19.622891</v>
       </c>
       <c r="M141" t="n">
-        <v>10.12</v>
+        <v>19.18</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
@@ -8348,10 +8362,10 @@
         <v>181</v>
       </c>
       <c r="E142" t="n">
-        <v>3128</v>
+        <v>3131</v>
       </c>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -8369,16 +8383,16 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>45247.17200462607</v>
+        <v>45247.17362783635</v>
       </c>
       <c r="L142" t="n">
-        <v>19.622891</v>
+        <v>10.832219</v>
       </c>
       <c r="M142" t="n">
-        <v>19.18</v>
+        <v>9.92</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
@@ -8404,10 +8418,10 @@
         <v>181</v>
       </c>
       <c r="E143" t="n">
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="F143" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -8425,16 +8439,16 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>45247.17362783635</v>
+        <v>45247.17441298727</v>
       </c>
       <c r="L143" t="n">
-        <v>10.832219</v>
+        <v>11.333606</v>
       </c>
       <c r="M143" t="n">
-        <v>9.92</v>
+        <v>9.49</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -8460,10 +8474,10 @@
         <v>181</v>
       </c>
       <c r="E144" t="n">
-        <v>3132</v>
+        <v>3136</v>
       </c>
       <c r="F144" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -8481,16 +8495,16 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>45247.17441298727</v>
+        <v>45247.1778355942</v>
       </c>
       <c r="L144" t="n">
-        <v>11.333606</v>
+        <v>23.158118</v>
       </c>
       <c r="M144" t="n">
-        <v>9.49</v>
+        <v>19.61</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
@@ -8516,10 +8530,10 @@
         <v>181</v>
       </c>
       <c r="E145" t="n">
-        <v>3136</v>
+        <v>3141</v>
       </c>
       <c r="F145" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -8537,16 +8551,16 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>45247.1778355942</v>
+        <v>45247.18148614821</v>
       </c>
       <c r="L145" t="n">
-        <v>23.158118</v>
+        <v>10.152876</v>
       </c>
       <c r="M145" t="n">
-        <v>19.61</v>
+        <v>8.09</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -8557,29 +8571,29 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D146" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E146" t="n">
-        <v>3141</v>
+        <v>3172</v>
       </c>
       <c r="F146" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -8589,24 +8603,28 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Added from Corrections</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>1723</v>
-      </c>
-      <c r="K146" s="2" t="n">
-        <v>45247.18148614821</v>
-      </c>
-      <c r="L146" t="n">
-        <v>10.152876</v>
+        <v>3471</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
       </c>
       <c r="M146" t="n">
-        <v>8.09</v>
+        <v>11.13</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Corrected: ResponseTime</t>
+          <t>Added from Corrections</t>
         </is>
       </c>
     </row>
@@ -8628,10 +8646,10 @@
         <v>184</v>
       </c>
       <c r="E147" t="n">
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -8649,7 +8667,7 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>3471</v>
+        <v>3472</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -8662,7 +8680,7 @@
         </is>
       </c>
       <c r="M147" t="n">
-        <v>11.13</v>
+        <v>12.67</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
@@ -8688,10 +8706,10 @@
         <v>184</v>
       </c>
       <c r="E148" t="n">
-        <v>3173</v>
+        <v>3174</v>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -8709,7 +8727,7 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>3472</v>
+        <v>3473</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -8722,7 +8740,7 @@
         </is>
       </c>
       <c r="M148" t="n">
-        <v>12.67</v>
+        <v>11.73</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
@@ -8748,10 +8766,10 @@
         <v>184</v>
       </c>
       <c r="E149" t="n">
-        <v>3174</v>
+        <v>3175</v>
       </c>
       <c r="F149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -8769,7 +8787,7 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>3473</v>
+        <v>3474</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -8782,7 +8800,7 @@
         </is>
       </c>
       <c r="M149" t="n">
-        <v>11.73</v>
+        <v>14</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
@@ -8808,10 +8826,10 @@
         <v>184</v>
       </c>
       <c r="E150" t="n">
-        <v>3175</v>
+        <v>3176</v>
       </c>
       <c r="F150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -8829,7 +8847,7 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>3474</v>
+        <v>3475</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -8842,7 +8860,7 @@
         </is>
       </c>
       <c r="M150" t="n">
-        <v>14</v>
+        <v>12.4</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
@@ -8868,10 +8886,10 @@
         <v>184</v>
       </c>
       <c r="E151" t="n">
-        <v>3176</v>
+        <v>3177</v>
       </c>
       <c r="F151" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -8889,7 +8907,7 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -8902,7 +8920,7 @@
         </is>
       </c>
       <c r="M151" t="n">
-        <v>12.4</v>
+        <v>12.94</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
@@ -8928,10 +8946,10 @@
         <v>184</v>
       </c>
       <c r="E152" t="n">
-        <v>3177</v>
+        <v>3178</v>
       </c>
       <c r="F152" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -8949,7 +8967,7 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -8962,7 +8980,7 @@
         </is>
       </c>
       <c r="M152" t="n">
-        <v>12.94</v>
+        <v>12.37</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
@@ -8988,10 +9006,10 @@
         <v>184</v>
       </c>
       <c r="E153" t="n">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="F153" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -9009,7 +9027,7 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -9022,7 +9040,7 @@
         </is>
       </c>
       <c r="M153" t="n">
-        <v>12.37</v>
+        <v>26.7</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
@@ -9048,10 +9066,10 @@
         <v>184</v>
       </c>
       <c r="E154" t="n">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="F154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -9069,7 +9087,7 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>3478</v>
+        <v>3479</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -9082,7 +9100,7 @@
         </is>
       </c>
       <c r="M154" t="n">
-        <v>26.7</v>
+        <v>16.89</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
@@ -9108,10 +9126,10 @@
         <v>184</v>
       </c>
       <c r="E155" t="n">
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="F155" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -9129,7 +9147,7 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>3479</v>
+        <v>3480</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -9142,7 +9160,7 @@
         </is>
       </c>
       <c r="M155" t="n">
-        <v>16.89</v>
+        <v>11.99</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
@@ -9168,10 +9186,10 @@
         <v>184</v>
       </c>
       <c r="E156" t="n">
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="F156" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -9180,7 +9198,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9189,7 +9207,7 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -9202,7 +9220,7 @@
         </is>
       </c>
       <c r="M156" t="n">
-        <v>11.99</v>
+        <v>30</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
@@ -9228,10 +9246,10 @@
         <v>184</v>
       </c>
       <c r="E157" t="n">
-        <v>3182</v>
+        <v>3183</v>
       </c>
       <c r="F157" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -9249,7 +9267,7 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -9288,10 +9306,10 @@
         <v>184</v>
       </c>
       <c r="E158" t="n">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="F158" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -9309,7 +9327,7 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>3482</v>
+        <v>3483</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -9348,10 +9366,10 @@
         <v>184</v>
       </c>
       <c r="E159" t="n">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="F159" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -9369,7 +9387,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>3483</v>
+        <v>3484</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -9408,10 +9426,10 @@
         <v>184</v>
       </c>
       <c r="E160" t="n">
-        <v>3185</v>
+        <v>3186</v>
       </c>
       <c r="F160" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -9429,7 +9447,7 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>3484</v>
+        <v>3485</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -9468,10 +9486,10 @@
         <v>184</v>
       </c>
       <c r="E161" t="n">
-        <v>3186</v>
+        <v>3187</v>
       </c>
       <c r="F161" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -9489,7 +9507,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -9528,10 +9546,10 @@
         <v>184</v>
       </c>
       <c r="E162" t="n">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="F162" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -9549,7 +9567,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>3486</v>
+        <v>3487</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -9588,10 +9606,10 @@
         <v>184</v>
       </c>
       <c r="E163" t="n">
-        <v>3188</v>
+        <v>3189</v>
       </c>
       <c r="F163" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -9609,7 +9627,7 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>3487</v>
+        <v>3488</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -9648,10 +9666,10 @@
         <v>184</v>
       </c>
       <c r="E164" t="n">
-        <v>3189</v>
+        <v>3190</v>
       </c>
       <c r="F164" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -9669,7 +9687,7 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>3488</v>
+        <v>3489</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -9708,10 +9726,10 @@
         <v>184</v>
       </c>
       <c r="E165" t="n">
-        <v>3190</v>
+        <v>3191</v>
       </c>
       <c r="F165" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -9729,7 +9747,7 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>3489</v>
+        <v>3490</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -9745,66 +9763,6 @@
         <v>30</v>
       </c>
       <c r="N165" t="inlineStr">
-        <is>
-          <t>Added from Corrections</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>yoshi</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>15</v>
-      </c>
-      <c r="D166" t="n">
-        <v>184</v>
-      </c>
-      <c r="E166" t="n">
-        <v>3191</v>
-      </c>
-      <c r="F166" t="n">
-        <v>20</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Added from Corrections</t>
-        </is>
-      </c>
-      <c r="J166" t="n">
-        <v>3490</v>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="M166" t="n">
-        <v>30</v>
-      </c>
-      <c r="N166" t="inlineStr">
         <is>
           <t>Added from Corrections</t>
         </is>
